--- a/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 2.xlsx
+++ b/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 2.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24729"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{40748617-228E-4BA3-B83B-C91BCD6D5633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="11070"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -110,7 +109,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
@@ -270,34 +269,34 @@
     <xf numFmtId="41" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="41" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="41" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -395,23 +394,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -447,23 +429,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -639,7 +604,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:J18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -697,13 +662,24 @@
       <c r="D3" s="7">
         <v>5800000</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="8"/>
+      <c r="E3" s="5">
+        <v>3</v>
+      </c>
+      <c r="F3" s="8">
+        <f>D3*E3</f>
+        <v>17400000</v>
+      </c>
       <c r="G3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="7"/>
-      <c r="I3" s="8"/>
+      <c r="H3" s="7">
+        <f>IF(G3="T",F3*0.03,0)</f>
+        <v>522000</v>
+      </c>
+      <c r="I3" s="8">
+        <f>F3-H3</f>
+        <v>16878000</v>
+      </c>
       <c r="J3" s="9"/>
     </row>
     <row r="4" spans="2:10" ht="20.25" x14ac:dyDescent="0.35">
@@ -716,13 +692,24 @@
       <c r="D4" s="7">
         <v>3500000</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="8"/>
+      <c r="E4" s="5">
+        <v>3</v>
+      </c>
+      <c r="F4" s="8">
+        <f t="shared" ref="F4:F12" si="0">D4*E4</f>
+        <v>10500000</v>
+      </c>
       <c r="G4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="7"/>
-      <c r="I4" s="8"/>
+      <c r="H4" s="7">
+        <f t="shared" ref="H4:H12" si="1">IF(G4="T",F4*0.03,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="8">
+        <f t="shared" ref="I4:I13" si="2">F4-H4</f>
+        <v>10500000</v>
+      </c>
       <c r="J4" s="9"/>
     </row>
     <row r="5" spans="2:10" ht="20.25" x14ac:dyDescent="0.35">
@@ -735,13 +722,24 @@
       <c r="D5" s="7">
         <v>5799000</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="8"/>
+      <c r="E5" s="5">
+        <v>5</v>
+      </c>
+      <c r="F5" s="8">
+        <f t="shared" si="0"/>
+        <v>28995000</v>
+      </c>
       <c r="G5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="8"/>
+      <c r="H5" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I5" s="8">
+        <f t="shared" si="2"/>
+        <v>28995000</v>
+      </c>
       <c r="J5" s="9"/>
     </row>
     <row r="6" spans="2:10" ht="20.25" x14ac:dyDescent="0.35">
@@ -754,13 +752,24 @@
       <c r="D6" s="7">
         <v>4050000</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="8"/>
+      <c r="E6" s="5">
+        <v>6</v>
+      </c>
+      <c r="F6" s="8">
+        <f t="shared" si="0"/>
+        <v>24300000</v>
+      </c>
       <c r="G6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="8"/>
+      <c r="H6" s="7">
+        <f t="shared" si="1"/>
+        <v>729000</v>
+      </c>
+      <c r="I6" s="8">
+        <f t="shared" si="2"/>
+        <v>23571000</v>
+      </c>
       <c r="J6" s="9"/>
     </row>
     <row r="7" spans="2:10" ht="20.25" x14ac:dyDescent="0.35">
@@ -773,13 +782,24 @@
       <c r="D7" s="7">
         <v>696000</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="8"/>
+      <c r="E7" s="5">
+        <v>2</v>
+      </c>
+      <c r="F7" s="8">
+        <f t="shared" si="0"/>
+        <v>1392000</v>
+      </c>
       <c r="G7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
+      <c r="H7" s="7">
+        <f t="shared" si="1"/>
+        <v>41760</v>
+      </c>
+      <c r="I7" s="8">
+        <f t="shared" si="2"/>
+        <v>1350240</v>
+      </c>
       <c r="J7" s="9"/>
     </row>
     <row r="8" spans="2:10" ht="20.25" x14ac:dyDescent="0.35">
@@ -792,13 +812,24 @@
       <c r="D8" s="7">
         <v>1199000</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="8"/>
+      <c r="E8" s="5">
+        <v>1</v>
+      </c>
+      <c r="F8" s="8">
+        <f t="shared" si="0"/>
+        <v>1199000</v>
+      </c>
       <c r="G8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="7"/>
-      <c r="I8" s="8"/>
+      <c r="H8" s="7">
+        <f t="shared" si="1"/>
+        <v>35970</v>
+      </c>
+      <c r="I8" s="8">
+        <f t="shared" si="2"/>
+        <v>1163030</v>
+      </c>
       <c r="J8" s="9"/>
     </row>
     <row r="9" spans="2:10" ht="20.25" x14ac:dyDescent="0.35">
@@ -811,13 +842,24 @@
       <c r="D9" s="7">
         <v>1365000</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="8"/>
+      <c r="E9" s="5">
+        <v>4</v>
+      </c>
+      <c r="F9" s="8">
+        <f t="shared" si="0"/>
+        <v>5460000</v>
+      </c>
       <c r="G9" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="8"/>
+      <c r="H9" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="8">
+        <f t="shared" si="2"/>
+        <v>5460000</v>
+      </c>
       <c r="J9" s="9"/>
     </row>
     <row r="10" spans="2:10" ht="20.25" x14ac:dyDescent="0.35">
@@ -830,13 +872,24 @@
       <c r="D10" s="7">
         <v>845000</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="8"/>
+      <c r="E10" s="5">
+        <v>5</v>
+      </c>
+      <c r="F10" s="8">
+        <f t="shared" si="0"/>
+        <v>4225000</v>
+      </c>
       <c r="G10" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H10" s="7"/>
-      <c r="I10" s="8"/>
+      <c r="H10" s="7">
+        <f t="shared" si="1"/>
+        <v>126750</v>
+      </c>
+      <c r="I10" s="8">
+        <f t="shared" si="2"/>
+        <v>4098250</v>
+      </c>
       <c r="J10" s="9"/>
     </row>
     <row r="11" spans="2:10" ht="20.25" x14ac:dyDescent="0.35">
@@ -849,13 +902,24 @@
       <c r="D11" s="7">
         <v>1303250</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="8"/>
+      <c r="E11" s="5">
+        <v>7</v>
+      </c>
+      <c r="F11" s="8">
+        <f t="shared" si="0"/>
+        <v>9122750</v>
+      </c>
       <c r="G11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="8"/>
+      <c r="H11" s="7">
+        <f t="shared" si="1"/>
+        <v>273682.5</v>
+      </c>
+      <c r="I11" s="8">
+        <f t="shared" si="2"/>
+        <v>8849067.5</v>
+      </c>
       <c r="J11" s="9"/>
     </row>
     <row r="12" spans="2:10" ht="20.25" x14ac:dyDescent="0.35">
@@ -868,26 +932,49 @@
       <c r="D12" s="7">
         <v>1099000</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="8"/>
+      <c r="E12" s="5">
+        <v>8</v>
+      </c>
+      <c r="F12" s="8">
+        <f t="shared" si="0"/>
+        <v>8792000</v>
+      </c>
       <c r="G12" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="7"/>
-      <c r="I12" s="8"/>
+      <c r="H12" s="7">
+        <f t="shared" si="1"/>
+        <v>263760</v>
+      </c>
+      <c r="I12" s="8">
+        <f t="shared" si="2"/>
+        <v>8528240</v>
+      </c>
       <c r="J12" s="9"/>
     </row>
     <row r="13" spans="2:10" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="13">
+        <f>SUM(E3:E12)</f>
+        <v>44</v>
+      </c>
+      <c r="F13" s="16">
+        <f>SUM(F3:F12)</f>
+        <v>111385750</v>
+      </c>
+      <c r="G13" s="12"/>
+      <c r="H13" s="14">
+        <f>SUM(H3:H12)</f>
+        <v>1992922.5</v>
+      </c>
+      <c r="I13" s="14">
+        <f t="shared" si="2"/>
+        <v>109392827.5</v>
+      </c>
     </row>
     <row r="15" spans="2:10" ht="20.25" x14ac:dyDescent="0.35">
       <c r="B15" s="1" t="s">
@@ -895,42 +982,42 @@
       </c>
     </row>
     <row r="16" spans="2:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
     </row>
     <row r="18" spans="2:9" ht="20.25" x14ac:dyDescent="0.35">
       <c r="B18" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="1"/>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="23" t="s">
+      <c r="E18" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -939,7 +1026,7 @@
     <mergeCell ref="E18:I18"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E18" r:id="rId1" xr:uid="{A3EA2D7D-C974-48E7-8FA5-1A669151729B}"/>
+    <hyperlink ref="E18" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>

--- a/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 2.xlsx
+++ b/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 2.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24729"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{40748617-228E-4BA3-B83B-C91BCD6D5633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="11070"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -109,7 +110,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
@@ -269,34 +270,34 @@
     <xf numFmtId="41" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="41" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="41" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -394,6 +395,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -429,6 +447,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -604,7 +639,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:J18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -662,24 +697,13 @@
       <c r="D3" s="7">
         <v>5800000</v>
       </c>
-      <c r="E3" s="5">
-        <v>3</v>
-      </c>
-      <c r="F3" s="8">
-        <f>D3*E3</f>
-        <v>17400000</v>
-      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="8"/>
       <c r="G3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="7">
-        <f>IF(G3="T",F3*0.03,0)</f>
-        <v>522000</v>
-      </c>
-      <c r="I3" s="8">
-        <f>F3-H3</f>
-        <v>16878000</v>
-      </c>
+      <c r="H3" s="7"/>
+      <c r="I3" s="8"/>
       <c r="J3" s="9"/>
     </row>
     <row r="4" spans="2:10" ht="20.25" x14ac:dyDescent="0.35">
@@ -692,24 +716,13 @@
       <c r="D4" s="7">
         <v>3500000</v>
       </c>
-      <c r="E4" s="5">
-        <v>3</v>
-      </c>
-      <c r="F4" s="8">
-        <f t="shared" ref="F4:F12" si="0">D4*E4</f>
-        <v>10500000</v>
-      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="8"/>
       <c r="G4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="7">
-        <f t="shared" ref="H4:H12" si="1">IF(G4="T",F4*0.03,0)</f>
-        <v>0</v>
-      </c>
-      <c r="I4" s="8">
-        <f t="shared" ref="I4:I13" si="2">F4-H4</f>
-        <v>10500000</v>
-      </c>
+      <c r="H4" s="7"/>
+      <c r="I4" s="8"/>
       <c r="J4" s="9"/>
     </row>
     <row r="5" spans="2:10" ht="20.25" x14ac:dyDescent="0.35">
@@ -722,24 +735,13 @@
       <c r="D5" s="7">
         <v>5799000</v>
       </c>
-      <c r="E5" s="5">
-        <v>5</v>
-      </c>
-      <c r="F5" s="8">
-        <f t="shared" si="0"/>
-        <v>28995000</v>
-      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="8"/>
       <c r="G5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I5" s="8">
-        <f t="shared" si="2"/>
-        <v>28995000</v>
-      </c>
+      <c r="H5" s="7"/>
+      <c r="I5" s="8"/>
       <c r="J5" s="9"/>
     </row>
     <row r="6" spans="2:10" ht="20.25" x14ac:dyDescent="0.35">
@@ -752,24 +754,13 @@
       <c r="D6" s="7">
         <v>4050000</v>
       </c>
-      <c r="E6" s="5">
-        <v>6</v>
-      </c>
-      <c r="F6" s="8">
-        <f t="shared" si="0"/>
-        <v>24300000</v>
-      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="8"/>
       <c r="G6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="7">
-        <f t="shared" si="1"/>
-        <v>729000</v>
-      </c>
-      <c r="I6" s="8">
-        <f t="shared" si="2"/>
-        <v>23571000</v>
-      </c>
+      <c r="H6" s="7"/>
+      <c r="I6" s="8"/>
       <c r="J6" s="9"/>
     </row>
     <row r="7" spans="2:10" ht="20.25" x14ac:dyDescent="0.35">
@@ -782,24 +773,13 @@
       <c r="D7" s="7">
         <v>696000</v>
       </c>
-      <c r="E7" s="5">
-        <v>2</v>
-      </c>
-      <c r="F7" s="8">
-        <f t="shared" si="0"/>
-        <v>1392000</v>
-      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="8"/>
       <c r="G7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="7">
-        <f t="shared" si="1"/>
-        <v>41760</v>
-      </c>
-      <c r="I7" s="8">
-        <f t="shared" si="2"/>
-        <v>1350240</v>
-      </c>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8"/>
       <c r="J7" s="9"/>
     </row>
     <row r="8" spans="2:10" ht="20.25" x14ac:dyDescent="0.35">
@@ -812,24 +792,13 @@
       <c r="D8" s="7">
         <v>1199000</v>
       </c>
-      <c r="E8" s="5">
-        <v>1</v>
-      </c>
-      <c r="F8" s="8">
-        <f t="shared" si="0"/>
-        <v>1199000</v>
-      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="8"/>
       <c r="G8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="7">
-        <f t="shared" si="1"/>
-        <v>35970</v>
-      </c>
-      <c r="I8" s="8">
-        <f t="shared" si="2"/>
-        <v>1163030</v>
-      </c>
+      <c r="H8" s="7"/>
+      <c r="I8" s="8"/>
       <c r="J8" s="9"/>
     </row>
     <row r="9" spans="2:10" ht="20.25" x14ac:dyDescent="0.35">
@@ -842,24 +811,13 @@
       <c r="D9" s="7">
         <v>1365000</v>
       </c>
-      <c r="E9" s="5">
-        <v>4</v>
-      </c>
-      <c r="F9" s="8">
-        <f t="shared" si="0"/>
-        <v>5460000</v>
-      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="8"/>
       <c r="G9" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="8">
-        <f t="shared" si="2"/>
-        <v>5460000</v>
-      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="8"/>
       <c r="J9" s="9"/>
     </row>
     <row r="10" spans="2:10" ht="20.25" x14ac:dyDescent="0.35">
@@ -872,24 +830,13 @@
       <c r="D10" s="7">
         <v>845000</v>
       </c>
-      <c r="E10" s="5">
-        <v>5</v>
-      </c>
-      <c r="F10" s="8">
-        <f t="shared" si="0"/>
-        <v>4225000</v>
-      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="8"/>
       <c r="G10" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H10" s="7">
-        <f t="shared" si="1"/>
-        <v>126750</v>
-      </c>
-      <c r="I10" s="8">
-        <f t="shared" si="2"/>
-        <v>4098250</v>
-      </c>
+      <c r="H10" s="7"/>
+      <c r="I10" s="8"/>
       <c r="J10" s="9"/>
     </row>
     <row r="11" spans="2:10" ht="20.25" x14ac:dyDescent="0.35">
@@ -902,24 +849,13 @@
       <c r="D11" s="7">
         <v>1303250</v>
       </c>
-      <c r="E11" s="5">
-        <v>7</v>
-      </c>
-      <c r="F11" s="8">
-        <f t="shared" si="0"/>
-        <v>9122750</v>
-      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="8"/>
       <c r="G11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="7">
-        <f t="shared" si="1"/>
-        <v>273682.5</v>
-      </c>
-      <c r="I11" s="8">
-        <f t="shared" si="2"/>
-        <v>8849067.5</v>
-      </c>
+      <c r="H11" s="7"/>
+      <c r="I11" s="8"/>
       <c r="J11" s="9"/>
     </row>
     <row r="12" spans="2:10" ht="20.25" x14ac:dyDescent="0.35">
@@ -932,49 +868,26 @@
       <c r="D12" s="7">
         <v>1099000</v>
       </c>
-      <c r="E12" s="5">
-        <v>8</v>
-      </c>
-      <c r="F12" s="8">
-        <f t="shared" si="0"/>
-        <v>8792000</v>
-      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="8"/>
       <c r="G12" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="7">
-        <f t="shared" si="1"/>
-        <v>263760</v>
-      </c>
-      <c r="I12" s="8">
-        <f t="shared" si="2"/>
-        <v>8528240</v>
-      </c>
+      <c r="H12" s="7"/>
+      <c r="I12" s="8"/>
       <c r="J12" s="9"/>
     </row>
     <row r="13" spans="2:10" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="13">
-        <f>SUM(E3:E12)</f>
-        <v>44</v>
-      </c>
-      <c r="F13" s="16">
-        <f>SUM(F3:F12)</f>
-        <v>111385750</v>
-      </c>
-      <c r="G13" s="12"/>
-      <c r="H13" s="14">
-        <f>SUM(H3:H12)</f>
-        <v>1992922.5</v>
-      </c>
-      <c r="I13" s="14">
-        <f t="shared" si="2"/>
-        <v>109392827.5</v>
-      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
     </row>
     <row r="15" spans="2:10" ht="20.25" x14ac:dyDescent="0.35">
       <c r="B15" s="1" t="s">
@@ -982,42 +895,42 @@
       </c>
     </row>
     <row r="16" spans="2:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
     </row>
     <row r="18" spans="2:9" ht="20.25" x14ac:dyDescent="0.35">
       <c r="B18" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="1"/>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E18" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1026,7 +939,7 @@
     <mergeCell ref="E18:I18"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E18" r:id="rId1"/>
+    <hyperlink ref="E18" r:id="rId1" xr:uid="{A3EA2D7D-C974-48E7-8FA5-1A669151729B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
